--- a/public/static/员工档案导入模板.xlsx
+++ b/public/static/员工档案导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27240" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="员工档案" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>序号</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">员工工号
 </t>
     </r>
@@ -51,6 +59,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">姓名
 </t>
     </r>
@@ -68,6 +84,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">性别
 </t>
     </r>
@@ -85,6 +109,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">出生日期
 </t>
     </r>
@@ -102,6 +134,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">部门
 </t>
     </r>
@@ -119,6 +159,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">岗位
 </t>
     </r>
@@ -139,6 +187,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">员工类型
 </t>
     </r>
@@ -207,6 +263,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">个人手机号码
 </t>
     </r>
@@ -260,6 +324,9 @@
   </si>
   <si>
     <t>部门、岗位：输入对应的部门名称和岗位名称</t>
+  </si>
+  <si>
+    <t>部门：输入部门时请输入完整部门，如：宁波市镇海甬明轴承有限公司/仓库部</t>
   </si>
   <si>
     <t>直属主管：员工名称</t>
@@ -1317,34 +1384,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.5454545454545" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.81818181818182" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.54545454545455" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.27272727272727" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.18181818181818" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.27272727272727" style="2" customWidth="1"/>
-    <col min="8" max="10" width="8.09090909090909" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.36363636363636" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.0909090909091" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.72727272727273" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.5416666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.81666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="5.54166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.275" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.18333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.275" style="2" customWidth="1"/>
+    <col min="8" max="10" width="8.09166666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="6.36666666666667" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.0916666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.725" style="2" customWidth="1"/>
     <col min="14" max="14" width="10" style="2" customWidth="1"/>
-    <col min="15" max="15" width="4.63636363636364" style="2" customWidth="1"/>
-    <col min="16" max="16" width="6.81818181818182" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.2727272727273" style="2" customWidth="1"/>
-    <col min="18" max="19" width="7.54545454545455" style="2" customWidth="1"/>
-    <col min="20" max="20" width="9.54545454545454" style="2" customWidth="1"/>
-    <col min="21" max="21" width="10.8181818181818" style="2" customWidth="1"/>
-    <col min="22" max="22" width="10.5454545454545" style="2" customWidth="1"/>
-    <col min="23" max="25" width="12.9090909090909" style="2" customWidth="1"/>
-    <col min="26" max="26" width="10.4545454545455" style="2" customWidth="1"/>
-    <col min="27" max="29" width="12.9090909090909" style="2" customWidth="1"/>
+    <col min="15" max="15" width="4.63333333333333" style="2" customWidth="1"/>
+    <col min="16" max="16" width="6.81666666666667" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.275" style="2" customWidth="1"/>
+    <col min="18" max="19" width="7.54166666666667" style="2" customWidth="1"/>
+    <col min="20" max="20" width="9.54166666666667" style="2" customWidth="1"/>
+    <col min="21" max="21" width="10.8166666666667" style="2" customWidth="1"/>
+    <col min="22" max="22" width="10.5416666666667" style="2" customWidth="1"/>
+    <col min="23" max="25" width="12.9083333333333" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.4583333333333" style="2" customWidth="1"/>
+    <col min="27" max="29" width="12.9083333333333" style="2" customWidth="1"/>
     <col min="30" max="30" width="7" style="2" customWidth="1"/>
-    <col min="31" max="31" width="8.45454545454546" style="2" customWidth="1"/>
-    <col min="32" max="32" width="8.90909090909091" style="2" customWidth="1"/>
-    <col min="33" max="33" width="13.0909090909091" style="2" customWidth="1"/>
-    <col min="34" max="35" width="12.1818181818182" style="2" customWidth="1"/>
-    <col min="36" max="36" width="12.8181818181818" style="2" customWidth="1"/>
-    <col min="37" max="37" width="13.9090909090909" style="2" customWidth="1"/>
+    <col min="31" max="31" width="8.45833333333333" style="2" customWidth="1"/>
+    <col min="32" max="32" width="8.90833333333333" style="2" customWidth="1"/>
+    <col min="33" max="33" width="13.0916666666667" style="2" customWidth="1"/>
+    <col min="34" max="35" width="12.1833333333333" style="2" customWidth="1"/>
+    <col min="36" max="36" width="12.8166666666667" style="2" customWidth="1"/>
+    <col min="37" max="37" width="13.9083333333333" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="40" customHeight="1" spans="1:37">
@@ -1990,10 +2057,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A27"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="15.6"/>
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="84.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="84.4583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:1">
@@ -2051,7 +2118,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1" spans="1:1">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="13" ht="22" customHeight="1"/>
     <row r="14" ht="22" customHeight="1"/>
     <row r="15" ht="22" customHeight="1"/>
@@ -2067,6 +2138,7 @@
     <row r="25" ht="22" customHeight="1"/>
     <row r="26" ht="22" customHeight="1"/>
     <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/static/员工档案导入模板.xlsx
+++ b/public/static/员工档案导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27240" windowHeight="12165"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="员工档案" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>序号</t>
   </si>
@@ -109,14 +109,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">出生日期
 </t>
     </r>
@@ -321,6 +313,9 @@
   </si>
   <si>
     <t>员工工号：如果系统设置自动生成，则无需输入</t>
+  </si>
+  <si>
+    <t>出生日期格式：yyyy/MM/dd 示例：2024/9/10</t>
   </si>
   <si>
     <t>部门、岗位：输入对应的部门名称和岗位名称</t>
@@ -1384,20 +1379,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.5416666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.54166666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.275" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.18333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.275" style="2" customWidth="1"/>
-    <col min="8" max="10" width="8.09166666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.09166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.09166666666667" style="2" customWidth="1"/>
     <col min="11" max="11" width="6.36666666666667" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.0916666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="7.725" style="2" customWidth="1"/>
     <col min="14" max="14" width="10" style="2" customWidth="1"/>
-    <col min="15" max="15" width="4.63333333333333" style="2" customWidth="1"/>
-    <col min="16" max="16" width="6.81666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.275" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="2" customWidth="1"/>
+    <col min="17" max="17" width="21.75" style="2" customWidth="1"/>
     <col min="18" max="19" width="7.54166666666667" style="2" customWidth="1"/>
     <col min="20" max="20" width="9.54166666666667" style="2" customWidth="1"/>
     <col min="21" max="21" width="10.8166666666667" style="2" customWidth="1"/>
@@ -2057,7 +2054,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="84.4583333333333" customWidth="1"/>
@@ -2123,7 +2120,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1" spans="1:1">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
     <row r="14" ht="22" customHeight="1"/>
     <row r="15" ht="22" customHeight="1"/>
     <row r="16" ht="22" customHeight="1"/>
@@ -2139,6 +2140,7 @@
     <row r="26" ht="22" customHeight="1"/>
     <row r="27" ht="22" customHeight="1"/>
     <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/static/员工档案导入模板.xlsx
+++ b/public/static/员工档案导入模板.xlsx
@@ -109,6 +109,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">出生日期
 </t>
     </r>
@@ -1379,22 +1387,20 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.5416666666667" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.54166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.275" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.18333333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.275" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.09166666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.09166666666667" style="2" customWidth="1"/>
+    <col min="8" max="10" width="8.09166666666667" style="2" customWidth="1"/>
     <col min="11" max="11" width="6.36666666666667" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.0916666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="7.725" style="2" customWidth="1"/>
     <col min="14" max="14" width="10" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.5" style="2" customWidth="1"/>
-    <col min="17" max="17" width="21.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="4.63333333333333" style="2" customWidth="1"/>
+    <col min="16" max="16" width="6.81666666666667" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.275" style="2" customWidth="1"/>
     <col min="18" max="19" width="7.54166666666667" style="2" customWidth="1"/>
     <col min="20" max="20" width="9.54166666666667" style="2" customWidth="1"/>
     <col min="21" max="21" width="10.8166666666667" style="2" customWidth="1"/>
